--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="State" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,8 +487,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -506,8 +504,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -525,8 +521,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -544,8 +538,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -563,8 +555,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -582,8 +572,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -601,8 +589,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -620,8 +606,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -639,8 +623,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -658,8 +640,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -677,8 +657,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -696,8 +674,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -715,8 +691,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -734,8 +708,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -753,8 +725,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -772,8 +742,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -791,8 +759,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -810,8 +776,33 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>DUTAyRbiL6Y</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:46:59 UTC</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DUTAyRbiL6Y/</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>tawakkul</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -847,7 +838,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>reel</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,33 @@
         </is>
       </c>
       <c r="E21" t="inlineStr">
+        <is>
+          <t>tawakkul</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>DQblAfgjWBd</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-05-06 16:54:27 UTC</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQblAfgjWBd/</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
         <is>
           <t>tawakkul</t>
         </is>
@@ -838,7 +865,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reel</t>
+          <t>image</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="State" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -847,8 +847,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -866,8 +864,6 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -885,8 +881,33 @@
           <t>migrated</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DV6HcOBD1vh</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-05-07 04:24:42 UTC</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/reel/DV6HcOBD1vh/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -922,7 +943,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>reel</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,6 +904,33 @@
         </is>
       </c>
       <c r="E26" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>DSZ79AviI4k</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-05-07 15:16:23 UTC</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DSZ79AviI4k/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>general</t>
         </is>
@@ -943,7 +970,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reel</t>
+          <t>image</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,6 +931,33 @@
         </is>
       </c>
       <c r="E27" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DVg7TOwgOm9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-05-07 22:18:37 UTC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVg7TOwgOm9/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>general</t>
         </is>
@@ -970,7 +997,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>reel</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,6 +958,33 @@
         </is>
       </c>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DWR9Dv0AP2W</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-05-08 04:00:57 UTC</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWR9Dv0AP2W/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>general</t>
         </is>
@@ -997,7 +1024,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reel</t>
+          <t>image</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -987,6 +987,33 @@
       <c r="E29" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DQ9pqwaiAgi</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-05-08 14:24:58 UTC</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DQ9pqwaiAgi/</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>tawakkul</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1051,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>reel</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,6 +1014,33 @@
       <c r="E30" t="inlineStr">
         <is>
           <t>tawakkul</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DVqpeyjj-HF</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-05-09 04:05:16 UTC</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVqpeyjj-HF/</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>shukr</t>
         </is>
       </c>
     </row>
@@ -1051,7 +1078,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reel</t>
+          <t>image</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1039,6 +1039,33 @@
         </is>
       </c>
       <c r="E31" t="inlineStr">
+        <is>
+          <t>shukr</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DIV5HqgtZjX</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-05-09 14:01:08 UTC</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DIV5HqgtZjX/</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
         <is>
           <t>shukr</t>
         </is>
@@ -1078,7 +1105,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>reel</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1068,6 +1068,33 @@
       <c r="E32" t="inlineStr">
         <is>
           <t>shukr</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DVEQ7xaCN4w</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-05-10 04:34:10 UTC</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVEQ7xaCN4w/</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>
@@ -1105,7 +1132,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reel</t>
+          <t>image</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,6 +1093,33 @@
         </is>
       </c>
       <c r="E33" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>DHLRPCot7KT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-05-10 14:02:41 UTC</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DHLRPCot7KT/</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>general</t>
         </is>
@@ -1132,7 +1159,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>reel</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1120,6 +1120,33 @@
         </is>
       </c>
       <c r="E34" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>DUfzxNjjTqq</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-05-11 04:45:56 UTC</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DUfzxNjjTqq/</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
         <is>
           <t>general</t>
         </is>
@@ -1159,7 +1186,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reel</t>
+          <t>image</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1149,6 +1149,33 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DHlgjZutOmz</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-05-11 15:46:06 UTC</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DHlgjZutOmz/</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>dua</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1213,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>reel</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,6 +931,33 @@
         </is>
       </c>
       <c r="E27" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DVg7TOwgOm9</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-05-11 18:15:24 UTC</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVg7TOwgOm9/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
         <is>
           <t>general</t>
         </is>
@@ -970,7 +997,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>reel</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="State" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1176,6 +1176,141 @@
       <c r="E36" t="inlineStr">
         <is>
           <t>dua</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>DYEBevkEgW-</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:28:59 UTC</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYEBevkEgW-/</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>DX1E7SAK46i</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:31:54 UTC</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DX1E7SAK46i/</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DYGuEWpE4oj</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:33:17 UTC</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYGuEWpE4oj/</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>motivation</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DJ4DQK_TH23</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:41:08 UTC</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DJ4DQK_TH23/</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>DXwVc-pq6td</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-05-11 19:45:51 UTC</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXwVc-pq6td/</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1348,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>reel</t>
+          <t>image</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="State" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Repost Log" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="State" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1309,6 +1309,33 @@
         </is>
       </c>
       <c r="E41" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>DX6UX79mXrn</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-05-11 20:23:37 UTC</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DX6UX79mXrn/</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1336,6 +1336,33 @@
         </is>
       </c>
       <c r="E42" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DYML2xdKJcf</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-05-12 04:13:41 UTC</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYML2xdKJcf/</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1365,6 +1365,33 @@
       <c r="E43" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>DYJN6-gKaJ8</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-05-12 15:19:43 UTC</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYJN6-gKaJ8/</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>humor</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1392,6 +1392,33 @@
       <c r="E44" t="inlineStr">
         <is>
           <t>humor</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>DYKX8BgCspB</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:18:22 UTC</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYKX8BgCspB/</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1417,6 +1417,33 @@
         </is>
       </c>
       <c r="E45" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>DYE3kC6KnHk</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-05-12 19:20:43 UTC</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYE3kC6KnHk/</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1444,6 +1444,33 @@
         </is>
       </c>
       <c r="E46" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>DXTwJVoCoH5</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-05-13 04:28:56 UTC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXTwJVoCoH5/</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1471,6 +1471,33 @@
         </is>
       </c>
       <c r="E47" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>DXeMQ2ACh7Q</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2026-05-13 15:21:51 UTC</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXeMQ2ACh7Q/</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1498,6 +1498,33 @@
         </is>
       </c>
       <c r="E48" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>DXox7iXipCR</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2026-05-14 04:27:44 UTC</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXox7iXipCR/</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1525,6 +1525,33 @@
         </is>
       </c>
       <c r="E49" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>DXN-F8HijaB</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-05-14 15:04:28 UTC</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXN-F8HijaB/</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1552,6 +1552,33 @@
         </is>
       </c>
       <c r="E50" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>DXb56qBoCSl</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-05-15 04:34:26 UTC</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXb56qBoCSl/</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1579,6 +1579,33 @@
         </is>
       </c>
       <c r="E51" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>DXbNFW_ChSJ</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-05-15 14:45:43 UTC</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXbNFW_ChSJ/</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1608,6 +1608,33 @@
       <c r="E52" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>DYEBevkEgW-</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-05-16 04:08:48 UTC</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DYEBevkEgW-/</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1635,6 +1635,33 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>lifestyle</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>DS64ckCE_6I</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-05-16 14:04:30 UTC</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DS64ckCE_6I/</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>trending</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1662,6 +1662,33 @@
       <c r="E54" t="inlineStr">
         <is>
           <t>trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>DXRrEu1itTt</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-05-17 04:37:48 UTC</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXRrEu1itTt/</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1687,6 +1687,33 @@
         </is>
       </c>
       <c r="E55" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>DXjhJ5qitB6</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-05-17 14:03:12 UTC</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXjhJ5qitB6/</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1714,6 +1714,33 @@
         </is>
       </c>
       <c r="E56" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>DXozeevCr6z</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-05-18 04:50:27 UTC</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXozeevCr6z/</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,33 @@
         </is>
       </c>
       <c r="E57" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>DW87JdFivPP</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-05-18 16:01:37 UTC</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DW87JdFivPP/</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1768,6 +1768,33 @@
         </is>
       </c>
       <c r="E58" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>DW0ZEeYCk_T</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-05-19 04:41:06 UTC</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DW0ZEeYCk_T/</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,6 +1795,33 @@
         </is>
       </c>
       <c r="E59" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>DWyELFRCgyl</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-05-19 15:56:33 UTC</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWyELFRCgyl/</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1822,6 +1822,33 @@
         </is>
       </c>
       <c r="E60" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>DW-u4_uCq8S</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-05-20 04:44:37 UTC</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DW-u4_uCq8S/</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1849,6 +1849,33 @@
         </is>
       </c>
       <c r="E61" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>DXHZgu5CpvI</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-05-20 16:06:11 UTC</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXHZgu5CpvI/</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1876,6 +1876,33 @@
         </is>
       </c>
       <c r="E62" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>DXI9DUriko8</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-05-21 04:51:58 UTC</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXI9DUriko8/</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1905,6 +1905,33 @@
       <c r="E63" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>DXBJ6j5itdy</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-05-21 15:56:03 UTC</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXBJ6j5itdy/</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1932,6 +1932,33 @@
       <c r="E64" t="inlineStr">
         <is>
           <t>lifestyle</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>DW3aEqxCl7B</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-05-22 04:42:59 UTC</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DW3aEqxCl7B/</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1957,6 +1957,33 @@
         </is>
       </c>
       <c r="E65" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DXEdZt0ivt7</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-05-22 15:29:57 UTC</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXEdZt0ivt7/</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,6 +1984,33 @@
         </is>
       </c>
       <c r="E66" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DW6ES4_ChQf</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-05-23 04:14:28 UTC</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DW6ES4_ChQf/</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2011,6 +2011,33 @@
         </is>
       </c>
       <c r="E67" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DWtFm_kitAG</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-05-23 14:08:29 UTC</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWtFm_kitAG/</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2038,6 +2038,33 @@
         </is>
       </c>
       <c r="E68" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DXjjW_OioJA</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-05-24 04:46:53 UTC</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXjjW_OioJA/</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2065,6 +2065,33 @@
         </is>
       </c>
       <c r="E69" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DWneYLEimcS</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-05-24 14:07:08 UTC</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWneYLEimcS/</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2092,6 +2092,33 @@
         </is>
       </c>
       <c r="E70" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DWLKbqqiqVH</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-05-25 05:00:48 UTC</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWLKbqqiqVH/</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2119,6 +2119,33 @@
         </is>
       </c>
       <c r="E71" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DWViW3OCsHs</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-05-25 15:35:26 UTC</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWViW3OCsHs/</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2146,6 +2146,33 @@
         </is>
       </c>
       <c r="E72" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DWjL3NEirtS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-05-26 04:41:28 UTC</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWjL3NEirtS/</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2173,6 +2173,33 @@
         </is>
       </c>
       <c r="E73" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DWOIMysCkTg</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>2026-05-26 16:15:31 UTC</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWOIMysCkTg/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2200,6 +2200,33 @@
         </is>
       </c>
       <c r="E74" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DWlXkEiivCj</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>2026-05-27 04:55:37 UTC</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWlXkEiivCj/</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2227,6 +2227,33 @@
         </is>
       </c>
       <c r="E75" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DWqTbpSClOi</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>2026-05-27 16:24:43 UTC</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWqTbpSClOi/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2254,6 +2254,33 @@
         </is>
       </c>
       <c r="E76" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DWLUyZbioSe</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>2026-05-28 04:50:08 UTC</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWLUyZbioSe/</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2281,6 +2281,33 @@
         </is>
       </c>
       <c r="E77" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>DWyCz7lis57</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>2026-05-28 16:38:09 UTC</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWyCz7lis57/</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2308,6 +2308,33 @@
         </is>
       </c>
       <c r="E78" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>DX_NgjkqyHX</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>2026-05-29 04:51:50 UTC</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DX_NgjkqyHX/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2337,6 +2337,33 @@
       <c r="E79" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>DVpjr7_iu6G</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>2026-05-29 16:13:41 UTC</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVpjr7_iu6G/</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E80"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2364,6 +2364,33 @@
       <c r="E80" t="inlineStr">
         <is>
           <t>lifestyle</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>DVa49J3iltP</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>2026-05-30 04:33:05 UTC</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVa49J3iltP/</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2389,6 +2389,33 @@
         </is>
       </c>
       <c r="E81" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>DVs2WGNCi5D</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-05-30 14:13:05 UTC</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVs2WGNCi5D/</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E82"/>
+  <dimension ref="A1:E83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2416,6 +2416,33 @@
         </is>
       </c>
       <c r="E82" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>DVnLPHninGa</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-05-31 04:58:55 UTC</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVnLPHninGa/</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E83"/>
+  <dimension ref="A1:E84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2443,6 +2443,33 @@
         </is>
       </c>
       <c r="E83" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>DV1Fr72ilrd</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-05-31 14:17:55 UTC</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DV1Fr72ilrd/</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E84"/>
+  <dimension ref="A1:E85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2470,6 +2470,33 @@
         </is>
       </c>
       <c r="E84" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>DViQjivCsH-</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-06-01 05:23:58 UTC</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DViQjivCsH-/</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E85"/>
+  <dimension ref="A1:E86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2497,6 +2497,33 @@
         </is>
       </c>
       <c r="E85" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>DVa4rakCtR1</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-06-01 18:23:09 UTC</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVa4rakCtR1/</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E86"/>
+  <dimension ref="A1:E87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,6 +2524,33 @@
         </is>
       </c>
       <c r="E86" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>DWGpAf2ir3Z</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-06-02 05:09:15 UTC</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWGpAf2ir3Z/</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E87"/>
+  <dimension ref="A1:E88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2553,6 +2553,33 @@
       <c r="E87" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>DV2sc58Co-W</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-06-02 17:00:02 UTC</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DV2sc58Co-W/</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>trending</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2580,6 +2580,33 @@
       <c r="E88" t="inlineStr">
         <is>
           <t>trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>DWtZW2LCoG6</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-06-03 05:24:52 UTC</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWtZW2LCoG6/</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E89"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2605,6 +2605,33 @@
         </is>
       </c>
       <c r="E89" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>DVkuIxkiny4</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-06-03 17:25:39 UTC</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVkuIxkiny4/</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2632,6 +2632,33 @@
         </is>
       </c>
       <c r="E90" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>DV-hQ7HCl7k</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-06-04 05:20:16 UTC</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DV-hQ7HCl7k/</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E91"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2661,6 +2661,33 @@
       <c r="E91" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>DVqKrW8gbwp</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-06-04 15:56:44 UTC</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVqKrW8gbwp/</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>motivation</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2688,6 +2688,33 @@
       <c r="E92" t="inlineStr">
         <is>
           <t>motivation</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>DVN0kWVivuO</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-06-05 04:54:41 UTC</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVN0kWVivuO/</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E93"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2713,6 +2713,33 @@
         </is>
       </c>
       <c r="E93" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DVF3PepChr1</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-06-05 15:34:46 UTC</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVF3PepChr1/</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E94"/>
+  <dimension ref="A1:E95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2740,6 +2740,33 @@
         </is>
       </c>
       <c r="E94" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>DW21NOtirMQ</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-06-06 04:34:27 UTC</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DW21NOtirMQ/</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E95"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2769,6 +2769,33 @@
       <c r="E95" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>DXgstXMCqw1</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-06-06 14:16:04 UTC</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DXgstXMCqw1/</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>humor</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2796,6 +2796,33 @@
       <c r="E96" t="inlineStr">
         <is>
           <t>humor</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>DVS6Oemil8Z</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-06-07 05:04:47 UTC</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVS6Oemil8Z/</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2821,6 +2821,33 @@
         </is>
       </c>
       <c r="E97" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>DVLABJXiiXY</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-06-07 14:27:23 UTC</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVLABJXiiXY/</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2848,6 +2848,33 @@
         </is>
       </c>
       <c r="E98" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>DVOJv4Cim9g</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-06-08 05:11:08 UTC</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVOJv4Cim9g/</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E99"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2875,6 +2875,33 @@
         </is>
       </c>
       <c r="E99" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>DVA6vDfiqIE</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>2026-06-08 16:34:28 UTC</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVA6vDfiqIE/</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2902,6 +2902,33 @@
         </is>
       </c>
       <c r="E100" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>DVXwkVwiviQ</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>2026-06-09 04:44:13 UTC</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVXwkVwiviQ/</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2931,6 +2931,33 @@
       <c r="E101" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>DUpdqcKkvdp</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>2026-06-09 15:37:15 UTC</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DUpdqcKkvdp/</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>trending</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2958,6 +2958,33 @@
       <c r="E102" t="inlineStr">
         <is>
           <t>trending</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>DVasRFICnF6</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>2026-06-10 16:13:29 UTC</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVasRFICnF6/</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2983,6 +2983,33 @@
         </is>
       </c>
       <c r="E103" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DWwEG0ACmAC</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>2026-06-11 05:07:37 UTC</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWwEG0ACmAC/</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3010,6 +3010,33 @@
         </is>
       </c>
       <c r="E104" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>DWLJfpsikfs</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>2026-06-11 16:34:21 UTC</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DWLJfpsikfs/</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3037,6 +3037,33 @@
         </is>
       </c>
       <c r="E105" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>DUujKfIE6bO</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>2026-06-12 05:12:54 UTC</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DUujKfIE6bO/</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3064,6 +3064,33 @@
         </is>
       </c>
       <c r="E106" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>DU--wyGCvf5</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>2026-06-13 04:58:13 UTC</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DU--wyGCvf5/</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
         <is>
           <t>general</t>
         </is>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3093,6 +3093,33 @@
       <c r="E107" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>DUinHWPExCj</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>2026-06-13 14:35:56 UTC</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DUinHWPExCj/</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>lifestyle</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E108"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3120,6 +3120,33 @@
       <c r="E108" t="inlineStr">
         <is>
           <t>lifestyle</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>DUfGoIDExbS</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>2026-06-14 05:15:19 UTC</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DUfGoIDExbS/</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>general</t>
         </is>
       </c>
     </row>

--- a/data/tracker.xlsx
+++ b/data/tracker.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3147,6 +3147,33 @@
       <c r="E109" t="inlineStr">
         <is>
           <t>general</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>DVLGZUDChC0</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>reel</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>2026-06-14 14:38:23 UTC</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/p/DVLGZUDChC0/</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>humor</t>
         </is>
       </c>
     </row>
